--- a/PHY_SP_2025_N.xlsx
+++ b/PHY_SP_2025_N.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\BAC_SP_PREPA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46791033-D92E-484F-9380-A7605ADC25D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADFF639-8762-4F29-A855-52C4C9CDDEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,15 +66,6 @@
     <t>EXERCICE 3</t>
   </si>
   <si>
-    <t>1- Charge d'un condensateur par une source de courant. On veut déterminer la capacité $C_0$ d'un condensateur initialement déchargé. Le générateur de courant G débite un courant électrique d'intensité constante $I_0 = 1 \mu A$. A l'instant $t_0=0$, on met l'interrupteur K en position (1).</t>
-  </si>
-  <si>
-    <t>2- Décharge d'un condensateur dans un dipôle RL. Lorsque la tension aux bornes du condensateur prend la valeur $u_C = U_0 = 10 V$, on bascule K en position (2) à un nouvel instant $t_0=0$.</t>
-  </si>
-  <si>
-    <t>3- Sélection et démodulation d'une onde modulée en amplitude. On utilise une chaine électronique pour sélectionner et démoduler une onde électromagnétique modulée en amplitude, avec une diode D idéale, la bobine (b) et le condensateur $C_0$.</t>
-  </si>
-  <si>
     <t>EXERCICE 4</t>
   </si>
   <si>
@@ -108,121 +99,16 @@
     <t>SP-N2024-M1.png</t>
   </si>
   <si>
-    <t>2-1- Écrire, en utilisant les formules semi-développées, l'équation modélisant la réaction d'estérification qui se produit. Donner le nom de l'ester (E) formé.</t>
-  </si>
-  <si>
-    <t>2-2- Indiquer, en justifiant, la courbe correspondant à l'expérience (3).</t>
-  </si>
-  <si>
-    <t>2-4- Déterminer graphiquement $t_{1/2}$ le temps de demi-réaction correspondant à l'expérience (2).</t>
-  </si>
-  <si>
-    <t>2-5- Calculer le rendement de la réaction pour le cas de l'expérience (3).</t>
-  </si>
-  <si>
-    <t>1-1- Écrire l'équation chimique modélisant la réaction de dosage.</t>
-  </si>
-  <si>
-    <t>1-2- Déterminer la valeur de $C_A$.</t>
-  </si>
-  <si>
-    <t>1-3- Déduire que $C_0 = 4,80 mol.L^{-1}$.</t>
-  </si>
-  <si>
-    <t>1-4- Justifier si l'indication inscrite sur l'étiquette du flacon est vérifiée.</t>
-  </si>
-  <si>
-    <t>1-5- Déterminer la valeur de la constante d'équilibre $K$ associée à l'équation de la réaction de dosage.</t>
-  </si>
-  <si>
-    <t>1-6- En se basant sur le tableau d'avancement de la réaction de dosage à l'équivalence, trouver la concentration molaire $C_{eq}$ de la solution de sulfite de sodium $2Na^+_{(aq)} + SO^{2-}_{3(aq)}$ obtenue à l'équivalence.</t>
-  </si>
-  <si>
-    <t>2- Écrire l'équation de désintégration d'un noyau de cadmium en précisant le type de cette désintégration.</t>
-  </si>
-  <si>
-    <t>3- Un laboratoire reçoit à la date $t=0$ un échantillon de Cd d'activité $a_0 = 1,25 \cdot 10^{12} Bq$. A l'instant $t_1 = 2t_{1/2}$ l'activité de cet échantillon est $a_1$ et à l'instant $t_2 = 3 t_{1/2}$ son activité est $a_2$.</t>
-  </si>
-  <si>
-    <t>3-1- Établir l'expression $a_2 = \frac{a_1}{2}$.</t>
-  </si>
-  <si>
-    <t>3-2- Montrer que l'expression de $N_d$ le nombre de noyaux désintégrés entre les instants $t_1$ et $t_2$ est : $N_d = \frac{a_0 t_{1/2}}{8 \ln 2}$.</t>
-  </si>
-  <si>
-    <t>3-3- Déterminer, en unité MeV, la valeur de l'énergie libérée $E$ lors de la désintégration de cet échantillon entre les instants $t_1$ et $t_2$.</t>
-  </si>
-  <si>
     <t>Electricité(5 points)</t>
   </si>
   <si>
-    <t>1-1- Exprimer la tension $u_c(t)$ en fonction de $I_0$, $C_0$ et $t$.</t>
-  </si>
-  <si>
-    <t>1-2- Vérifier que $C_0 = 1 \mu F$.</t>
-  </si>
-  <si>
-    <t>2-1- Établir l'équation différentielle vérifiée par $u_c(t)$.</t>
-  </si>
-  <si>
-    <t>2-2-1- En exploitant la courbe de la figure 3, déterminer la valeur de la pseudopériode des oscillations.</t>
-  </si>
-  <si>
-    <t>2-2-2- En exploitant la courbe de la figure 3, déterminer le signe de l'intensité du courant $i$ entre l'instant $t_A$ et l'instant $t_B$.</t>
-  </si>
-  <si>
-    <t>2-3- Montrer que : $\frac{dE_T}{dt} = -ri^2$, avec $E_T$ l'énergie totale du circuit à un instant t.</t>
-  </si>
-  <si>
-    <t>2-4- Calculer $|E_{dh}|$ l'énergie dissipée par effet joule dans le circuit entre les instant $t=0$ et $t=t_A$.</t>
-  </si>
-  <si>
-    <t>3-1- Quel est le rôle de l'étage 2 ?</t>
-  </si>
-  <si>
-    <t>3-2- Trouver la valeur $C_1$ à laquelle il faut ajuster la capacité $C$ pour capter le signal modulé de fréquence $f_p = 162 kHz$ sachant que $L = 2 mH$ (on prend $\pi^2 = 10$).</t>
-  </si>
-  <si>
-    <t>3-3- La fréquence du signal modulant est $f_s = 5 kHz$. Si on ajuste R à la valeur $R_0 = 1,5 k\Omega$, aura-t-on une démodulation de bonne qualité ? Justifier.</t>
-  </si>
-  <si>
     <t>Mécanique (5,5 points)</t>
   </si>
   <si>
     <t>Les parties 1 et 2 sont indépendantes.</t>
   </si>
   <si>
-    <t>1- Ecrire l'expression vectorielle de la force d'attraction gravitationnelle $\vec{F}$ exercée par la Terre sur (S) dans la base de Freinet $(\vec{u}; \vec{n})$.</t>
-  </si>
-  <si>
-    <t>2- En appliquant la deuxième loi de Newton:</t>
-  </si>
-  <si>
     <t>Partie 1: Mouvement d'un satellite artificiel. Un satellite (S) de masse $m_s$ décrit une orbite circulaire autour de la Terre avec une période de révolution T à une altitude h. Données : $G = 6,67 \cdot 10^{-11} kg^{-1}.m^3.s^{-2}$ ; $R_T = 6380 km$ ; $T = 1 h 52 min$ ; $h = 1336 km$.</t>
-  </si>
-  <si>
-    <t>3- Calculer alors la valeur de la masse $m_T$.</t>
-  </si>
-  <si>
-    <t>2-1- Montrer que le mouvement circulaire du centre d'inertie $G_S$ autour de la Terre est uniforme.</t>
-  </si>
-  <si>
-    <t>2-2- Déterminer $V_S$ la norme de la vitesse de $G_S$ en fonction de $G$, $m_T$, $R_T$.</t>
-  </si>
-  <si>
-    <t>2-3- Déduire la relation : $\frac{T^2}{(R_T+h)^3} = k$ (k étant une constante), traduisant la troisième loi de Kepler.</t>
-  </si>
-  <si>
-    <t>1- En appliquant la deuxième loi de Newton, établir l'équation différentielle vérifiée par l'abscisse $x(t)$.</t>
-  </si>
-  <si>
-    <t>2- La solution de cette équation différentielle s'écrit $x(t) = X_m \cos(\frac{2\pi}{T_0}t + \varphi)$ avec $T_0$ la période propre de l'oscillateur.</t>
-  </si>
-  <si>
-    <t>2-1- Déterminer les valeurs de : $T_0$, $X_m$, $\varphi$.</t>
-  </si>
-  <si>
-    <t>2-2 Déduire la valeur de la raideur K (On prend $\pi^2 = 10$).</t>
   </si>
   <si>
     <t>Physique-Chimie</t>
@@ -256,21 +142,11 @@
 Les courbes de la figure représentent l'évolution temporelle de l'avancement $x$ de la réaction.</t>
   </si>
   <si>
-    <t>2-3- Répondre, en justifiant, par vrai ou faux à l'affirmation suivante : "La valeur de l'avancement final $x_f$ de la réaction sera la même pour les trois conditions expérimentales".</t>
-  </si>
-  <si>
     <t>On se propose dans cet exercice d'étudier la désintégration du cadmium 107. 
 Le cadmium radioactif $^{107}_{48}Cd$, donne, en se désintégrant, le noyau d'argent $^{107}_{47}Ag$ et une particule $e^+$ avec émission d'un rayonnement $\gamma$ (gamma). 
 Données : Masses: $m(^{107}_{48}Cd) = 106,88045 u$ ; $m(^{107}_{47}Ag) = 106,87947 u$ ; $m(^0_1e) = 5,486 \cdot 10^{-4} u$ ; Demi-vie du $^{107}_{48}Cd$ : $t_{1/2} = 6,93$ heures ; $1 u = 931,49 MeV.c^{-2}$.</t>
   </si>
   <si>
-    <t>1- Choisir parmi les affirmations suivantes l'affirmation juste : 
-(A): Dans le noyau $^{107}_{48}Cd$ il y a 59 protons. 
-(B): La désintégration d'un échantillon radioactif est d'autant plus rapide que sa constante radioactive $\lambda$ est plus petite. 
-(C): Dans le diagramme (N, Z) de Segré, les isotopes sont sur une ligne perpendiculaire à l'axe des Z. 
-(D): La cohésion du noyau est d'autant plus forte que son énergie de liaison par nucléon est petite.</t>
-  </si>
-  <si>
     <t>Les composantes électroniques telle que les diodes, les bobines, les condensateurs se trouvent dans différents circuits électriques et électroniques de plusieurs appareils... On se propose d'étudier : 
 la charge d'un condensateur et sa décharge dans un dipôle RL; 
 la sélection et la démodulation d'une onde modulée en amplitude.</t>
@@ -282,7 +158,131 @@
     <t>2)</t>
   </si>
   <si>
-    <t>3- Déterminer la variation de l'énergie potentielle élastique du système (solide (S) - ressort) entre les instants $t = 1 s$ et $t = 2,5 s$.</t>
+    <t>a) Écrire l'équation chimique modélisant la réaction de dosage.</t>
+  </si>
+  <si>
+    <t>b) Déterminer la valeur de $C_A$.</t>
+  </si>
+  <si>
+    <t>c) Déduire que $C_0 = 4,80 mol.L^{-1}$.</t>
+  </si>
+  <si>
+    <t>d) Justifier si l'indication inscrite sur l'étiquette du flacon est vérifiée.</t>
+  </si>
+  <si>
+    <t>e) Déterminer la valeur de la constante d'équilibre $K$ associée à l'équation de la réaction de dosage.</t>
+  </si>
+  <si>
+    <t>f) En se basant sur le tableau d'avancement de la réaction de dosage à l'équivalence, trouver la concentration molaire $C_{eq}$ de la solution de sulfite de sodium $2Na^+_{(aq)} + SO^{2-}_{3(aq)}$ obtenue à l'équivalence.</t>
+  </si>
+  <si>
+    <t>a) Écrire, en utilisant les formules semi-développées, l'équation modélisant la réaction d'estérification qui se produit. Donner le nom de l'ester (E) formé.</t>
+  </si>
+  <si>
+    <t>b) Indiquer, en justifiant, la courbe correspondant à l'expérience (3).</t>
+  </si>
+  <si>
+    <t>c) Répondre, en justifiant, par vrai ou faux à l'affirmation suivante : "La valeur de l'avancement final $x_f$ de la réaction sera la même pour les trois conditions expérimentales".</t>
+  </si>
+  <si>
+    <t>d) Déterminer graphiquement $t_{1/2}$ le temps de demi-réaction correspondant à l'expérience (2).</t>
+  </si>
+  <si>
+    <t>e) Calculer le rendement de la réaction pour le cas de l'expérience (3).</t>
+  </si>
+  <si>
+    <t>a) Établir l'expression $a_2 = \frac{a_1}{2}$.</t>
+  </si>
+  <si>
+    <t>b) Montrer que l'expression de $N_d$ le nombre de noyaux désintégrés entre les instants $t_1$ et $t_2$ est : $N_d = \frac{a_0 t_{1/2}}{8 \ln 2}$.</t>
+  </si>
+  <si>
+    <t>c) Déterminer, en unité MeV, la valeur de l'énergie libérée $E$ lors de la désintégration de cet échantillon entre les instants $t_1$ et $t_2$.</t>
+  </si>
+  <si>
+    <t>3) Un laboratoire reçoit à la date $t=0$ un échantillon de Cd d'activité $a_0 = 1,25 \cdot 10^{12} Bq$. A l'instant $t_1 = 2t_{1/2}$ l'activité de cet échantillon est $a_1$ et à l'instant $t_2 = 3 t_{1/2}$ son activité est $a_2$.</t>
+  </si>
+  <si>
+    <t>2) Écrire l'équation de désintégration d'un noyau de cadmium en précisant le type de cette désintégration.</t>
+  </si>
+  <si>
+    <t>1) Choisir parmi les affirmations suivantes l'affirmation juste : 
+&lt;br&gt;(A): Dans le noyau $^{107}_{48}Cd$ il y a 59 protons. 
+&lt;br&gt;(B): La désintégration d'un échantillon radioactif est d'autant plus rapide que sa constante radioactive $\lambda$ est plus petite. 
+&lt;br&gt;(C): Dans le diagramme (N, Z) de Segré, les isotopes sont sur une ligne perpendiculaire à l'axe des Z. 
+&lt;br&gt;(D): La cohésion du noyau est d'autant plus forte que son énergie de liaison par nucléon est petite.</t>
+  </si>
+  <si>
+    <t>1) Charge d'un condensateur par une source de courant. On veut déterminer la capacité $C_0$ d'un condensateur initialement déchargé. Le générateur de courant G débite un courant électrique d'intensité constante $I_0 = 1 \mu A$. A l'instant $t_0=0$, on met l'interrupteur K en position (1).</t>
+  </si>
+  <si>
+    <t>a) Exprimer la tension $u_c(t)$ en fonction de $I_0$, $C_0$ et $t$.</t>
+  </si>
+  <si>
+    <t>b) Vérifier que $C_0 = 1 \mu F$.</t>
+  </si>
+  <si>
+    <t>a) Établir l'équation différentielle vérifiée par $u_c(t)$.</t>
+  </si>
+  <si>
+    <t>2) Décharge d'un condensateur dans un dipôle RL. Lorsque la tension aux bornes du condensateur prend la valeur $u_C = U_0 = 10 V$, on bascule K en position (2) à un nouvel instant $t_0=0$.</t>
+  </si>
+  <si>
+    <t>b-1) En exploitant la courbe de la figure 3, déterminer la valeur de la pseudopériode des oscillations.</t>
+  </si>
+  <si>
+    <t>b-2) En exploitant la courbe de la figure 3, déterminer le signe de l'intensité du courant $i$ entre l'instant $t_A$ et l'instant $t_B$.</t>
+  </si>
+  <si>
+    <t>c) Montrer que : $\frac{dE_T}{dt} = -ri^2$, avec $E_T$ l'énergie totale du circuit à un instant t.</t>
+  </si>
+  <si>
+    <t>d) Calculer $|E_{dh}|$ l'énergie dissipée par effet joule dans le circuit entre les instant $t=0$ et $t=t_A$.</t>
+  </si>
+  <si>
+    <t>3) Sélection et démodulation d'une onde modulée en amplitude. On utilise une chaine électronique pour sélectionner et démoduler une onde électromagnétique modulée en amplitude, avec une diode D idéale, la bobine (b) et le condensateur $C_0$.</t>
+  </si>
+  <si>
+    <t>a) Quel est le rôle de l'étage 2 ?</t>
+  </si>
+  <si>
+    <t>b) Trouver la valeur $C_1$ à laquelle il faut ajuster la capacité $C$ pour capter le signal modulé de fréquence $f_p = 162 kHz$ sachant que $L = 2 mH$ (on prend $\pi^2 = 10$).</t>
+  </si>
+  <si>
+    <t>c) La fréquence du signal modulant est $f_s = 5 kHz$. Si on ajuste R à la valeur $R_0 = 1,5 k\Omega$, aura-t-on une démodulation de bonne qualité ? Justifier.</t>
+  </si>
+  <si>
+    <t>1) Ecrire l'expression vectorielle de la force d'attraction gravitationnelle $\vec{F}$ exercée par la Terre sur (S) dans la base de Freinet $(\vec{u}; \vec{n})$.</t>
+  </si>
+  <si>
+    <t>2) En appliquant la deuxième loi de Newton:</t>
+  </si>
+  <si>
+    <t>a) Montrer que le mouvement circulaire du centre d'inertie $G_S$ autour de la Terre est uniforme.</t>
+  </si>
+  <si>
+    <t>b) Déterminer $V_S$ la norme de la vitesse de $G_S$ en fonction de $G$, $m_T$, $R_T$.</t>
+  </si>
+  <si>
+    <t>c) Déduire la relation : $\frac{T^2}{(R_T+h)^3} = k$ (k étant une constante), traduisant la troisième loi de Kepler.</t>
+  </si>
+  <si>
+    <t>3) Calculer alors la valeur de la masse $m_T$.</t>
+  </si>
+  <si>
+    <t>1) En appliquant la deuxième loi de Newton, établir l'équation différentielle vérifiée par l'abscisse $x(t)$.</t>
+  </si>
+  <si>
+    <t>2) La solution de cette équation différentielle s'écrit $x(t) = X_m \cos(\frac{2\pi}{T_0}t + \varphi)$ avec $T_0$ la période propre de l'oscillateur.</t>
+  </si>
+  <si>
+    <t>a) Déterminer les valeurs de : $T_0$, $X_m$, $\varphi$.</t>
+  </si>
+  <si>
+    <t>b) Déduire la valeur de la raideur K (On prend $\pi^2 = 10$).</t>
+  </si>
+  <si>
+    <t>3) Déterminer la variation de l'énergie potentielle élastique du système (solide (S) - ressort) entre les instants $t = 1 s$ et $t = 2,5 s$.</t>
   </si>
 </sst>
 </file>
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -743,19 +743,19 @@
         <v>4</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -763,28 +763,28 @@
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I2" s="5">
         <v>2025</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="255" x14ac:dyDescent="0.25">
@@ -792,28 +792,28 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I3" s="5">
         <v>2025</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -821,32 +821,32 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I4" s="5">
         <v>2025</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -854,29 +854,29 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I5" s="5">
         <v>2025</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -884,29 +884,29 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I6" s="5">
         <v>2025</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -914,29 +914,29 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I7" s="5">
         <v>2025</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -944,29 +944,29 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>9</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I8" s="5">
         <v>2025</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
@@ -974,29 +974,29 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>9</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I9" s="5">
         <v>2025</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="150" x14ac:dyDescent="0.25">
@@ -1004,28 +1004,28 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I10" s="5">
         <v>2025</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -1033,32 +1033,32 @@
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>9</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I11" s="5">
         <v>2025</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -1066,29 +1066,29 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I12" s="5">
         <v>2025</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -1096,29 +1096,29 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I13" s="5">
         <v>2025</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -1126,29 +1126,29 @@
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>9</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I14" s="5">
         <v>2025</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -1156,29 +1156,29 @@
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I15" s="5">
         <v>2025</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="90" x14ac:dyDescent="0.25">
@@ -1186,42 +1186,42 @@
         <v>11</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I16" s="5">
         <v>2025</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
@@ -1229,16 +1229,16 @@
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I17" s="5">
         <v>2025</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -1246,13 +1246,13 @@
         <v>11</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
@@ -1260,16 +1260,16 @@
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I18" s="5">
         <v>2025</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -1277,32 +1277,32 @@
         <v>11</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I19" s="5">
         <v>2025</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -1310,29 +1310,29 @@
         <v>11</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I20" s="5">
         <v>2025</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -1340,29 +1340,29 @@
         <v>11</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I21" s="5">
         <v>2025</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="75" x14ac:dyDescent="0.25">
@@ -1370,28 +1370,28 @@
         <v>12</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I22" s="5">
         <v>2025</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -1399,32 +1399,32 @@
         <v>12</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I23" s="5">
         <v>2025</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -1432,29 +1432,29 @@
         <v>12</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I24" s="5">
         <v>2025</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -1462,32 +1462,32 @@
         <v>12</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I25" s="5">
         <v>2025</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -1495,59 +1495,59 @@
         <v>12</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I26" s="5">
         <v>2025</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I27" s="5">
         <v>2025</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -1555,29 +1555,29 @@
         <v>12</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I28" s="5">
         <v>2025</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -1585,29 +1585,29 @@
         <v>12</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I29" s="5">
         <v>2025</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -1615,32 +1615,32 @@
         <v>12</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I30" s="5">
         <v>2025</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -1648,29 +1648,29 @@
         <v>12</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>9</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I31" s="5">
         <v>2025</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -1678,101 +1678,101 @@
         <v>12</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I32" s="5">
         <v>2025</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I33" s="5">
         <v>2025</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I34" s="5">
         <v>2025</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3" t="s">
@@ -1780,123 +1780,123 @@
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I35" s="5">
         <v>2025</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I36" s="5">
         <v>2025</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>9</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I37" s="5">
         <v>2025</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>9</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I38" s="5">
         <v>2025</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
@@ -1904,59 +1904,59 @@
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I39" s="5">
         <v>2025</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="5"/>
       <c r="H40" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I40" s="5">
         <v>2025</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
@@ -1964,89 +1964,89 @@
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I41" s="5">
         <v>2025</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>9</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I42" s="5">
         <v>2025</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I43" s="5">
         <v>2025</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>7</v>
@@ -2060,16 +2060,16 @@
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I44" s="5">
         <v>2025</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/PHY_SP_2025_N.xlsx
+++ b/PHY_SP_2025_N.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\BAC_SP_PREPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADFF639-8762-4F29-A855-52C4C9CDDEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD88BE16-3685-433E-A7FF-C550BD921FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -228,18 +228,6 @@
     <t>2) Décharge d'un condensateur dans un dipôle RL. Lorsque la tension aux bornes du condensateur prend la valeur $u_C = U_0 = 10 V$, on bascule K en position (2) à un nouvel instant $t_0=0$.</t>
   </si>
   <si>
-    <t>b-1) En exploitant la courbe de la figure 3, déterminer la valeur de la pseudopériode des oscillations.</t>
-  </si>
-  <si>
-    <t>b-2) En exploitant la courbe de la figure 3, déterminer le signe de l'intensité du courant $i$ entre l'instant $t_A$ et l'instant $t_B$.</t>
-  </si>
-  <si>
-    <t>c) Montrer que : $\frac{dE_T}{dt} = -ri^2$, avec $E_T$ l'énergie totale du circuit à un instant t.</t>
-  </si>
-  <si>
-    <t>d) Calculer $|E_{dh}|$ l'énergie dissipée par effet joule dans le circuit entre les instant $t=0$ et $t=t_A$.</t>
-  </si>
-  <si>
     <t>3) Sélection et démodulation d'une onde modulée en amplitude. On utilise une chaine électronique pour sélectionner et démoduler une onde électromagnétique modulée en amplitude, avec une diode D idéale, la bobine (b) et le condensateur $C_0$.</t>
   </si>
   <si>
@@ -283,6 +271,18 @@
   </si>
   <si>
     <t>3) Déterminer la variation de l'énergie potentielle élastique du système (solide (S) - ressort) entre les instants $t = 1 s$ et $t = 2,5 s$.</t>
+  </si>
+  <si>
+    <t>b) En exploitant la courbe de la figure 3, déterminer la valeur de la pseudopériode des oscillations.</t>
+  </si>
+  <si>
+    <t>c) En exploitant la courbe de la figure 3, déterminer le signe de l'intensité du courant $i$ entre l'instant $t_A$ et l'instant $t_B$.</t>
+  </si>
+  <si>
+    <t>d) Montrer que : $\frac{dE_T}{dt} = -ri^2$, avec $E_T$ l'énergie totale du circuit à un instant t.</t>
+  </si>
+  <si>
+    <t>e) Calculer $|E_{dh}|$ l'énergie dissipée par effet joule dans le circuit entre les instant $t=0$ et $t=t_A$.</t>
   </si>
 </sst>
 </file>
@@ -315,12 +315,9 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -385,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -406,7 +403,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1282,7 +1282,7 @@
       <c r="C19" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="8" t="s">
         <v>52</v>
       </c>
       <c r="E19" s="3" t="s">
@@ -1404,7 +1404,7 @@
       <c r="C23" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="8" t="s">
         <v>55</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -1467,7 +1467,7 @@
       <c r="C25" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="8" t="s">
         <v>59</v>
       </c>
       <c r="E25" s="3" t="s">
@@ -1501,7 +1501,7 @@
         <v>7</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>8</v>
@@ -1531,7 +1531,7 @@
         <v>7</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>8</v>
@@ -1561,7 +1561,7 @@
         <v>7</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>8</v>
@@ -1620,11 +1620,11 @@
       <c r="C30" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>64</v>
+      <c r="D30" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>10</v>
@@ -1654,7 +1654,7 @@
         <v>7</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>9</v>
@@ -1684,7 +1684,7 @@
         <v>7</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
@@ -1772,7 +1772,7 @@
         <v>7</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3" t="s">
@@ -1802,11 +1802,11 @@
       <c r="C36" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D36" s="7" t="s">
-        <v>69</v>
+      <c r="D36" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>8</v>
@@ -1836,7 +1836,7 @@
         <v>7</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>9</v>
@@ -1866,7 +1866,7 @@
         <v>7</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>9</v>
@@ -1895,8 +1895,8 @@
       <c r="C39" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D39" s="8" t="s">
-        <v>73</v>
+      <c r="D39" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
@@ -1956,7 +1956,7 @@
         <v>7</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
@@ -1986,11 +1986,11 @@
       <c r="C42" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D42" s="7" t="s">
-        <v>75</v>
+      <c r="D42" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>9</v>
@@ -2022,7 +2022,7 @@
         <v>7</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>8</v>
@@ -2052,7 +2052,7 @@
         <v>7</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3" t="s">

--- a/PHY_SP_2025_N.xlsx
+++ b/PHY_SP_2025_N.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\BAC_SP_PREPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD88BE16-3685-433E-A7FF-C550BD921FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7830E9C3-26DA-4557-85AC-E15417EF22E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -206,83 +206,83 @@
     <t>2) Écrire l'équation de désintégration d'un noyau de cadmium en précisant le type de cette désintégration.</t>
   </si>
   <si>
-    <t>1) Choisir parmi les affirmations suivantes l'affirmation juste : 
-&lt;br&gt;(A): Dans le noyau $^{107}_{48}Cd$ il y a 59 protons. 
-&lt;br&gt;(B): La désintégration d'un échantillon radioactif est d'autant plus rapide que sa constante radioactive $\lambda$ est plus petite. 
-&lt;br&gt;(C): Dans le diagramme (N, Z) de Segré, les isotopes sont sur une ligne perpendiculaire à l'axe des Z. 
+    <t>1) Charge d'un condensateur par une source de courant. On veut déterminer la capacité $C_0$ d'un condensateur initialement déchargé. Le générateur de courant G débite un courant électrique d'intensité constante $I_0 = 1 \mu A$. A l'instant $t_0=0$, on met l'interrupteur K en position (1).</t>
+  </si>
+  <si>
+    <t>a) Exprimer la tension $u_c(t)$ en fonction de $I_0$, $C_0$ et $t$.</t>
+  </si>
+  <si>
+    <t>b) Vérifier que $C_0 = 1 \mu F$.</t>
+  </si>
+  <si>
+    <t>a) Établir l'équation différentielle vérifiée par $u_c(t)$.</t>
+  </si>
+  <si>
+    <t>2) Décharge d'un condensateur dans un dipôle RL. Lorsque la tension aux bornes du condensateur prend la valeur $u_C = U_0 = 10 V$, on bascule K en position (2) à un nouvel instant $t_0=0$.</t>
+  </si>
+  <si>
+    <t>3) Sélection et démodulation d'une onde modulée en amplitude. On utilise une chaine électronique pour sélectionner et démoduler une onde électromagnétique modulée en amplitude, avec une diode D idéale, la bobine (b) et le condensateur $C_0$.</t>
+  </si>
+  <si>
+    <t>a) Quel est le rôle de l'étage 2 ?</t>
+  </si>
+  <si>
+    <t>b) Trouver la valeur $C_1$ à laquelle il faut ajuster la capacité $C$ pour capter le signal modulé de fréquence $f_p = 162 kHz$ sachant que $L = 2 mH$ (on prend $\pi^2 = 10$).</t>
+  </si>
+  <si>
+    <t>c) La fréquence du signal modulant est $f_s = 5 kHz$. Si on ajuste R à la valeur $R_0 = 1,5 k\Omega$, aura-t-on une démodulation de bonne qualité ? Justifier.</t>
+  </si>
+  <si>
+    <t>1) Ecrire l'expression vectorielle de la force d'attraction gravitationnelle $\vec{F}$ exercée par la Terre sur (S) dans la base de Freinet $(\vec{u}; \vec{n})$.</t>
+  </si>
+  <si>
+    <t>2) En appliquant la deuxième loi de Newton:</t>
+  </si>
+  <si>
+    <t>a) Montrer que le mouvement circulaire du centre d'inertie $G_S$ autour de la Terre est uniforme.</t>
+  </si>
+  <si>
+    <t>b) Déterminer $V_S$ la norme de la vitesse de $G_S$ en fonction de $G$, $m_T$, $R_T$.</t>
+  </si>
+  <si>
+    <t>c) Déduire la relation : $\frac{T^2}{(R_T+h)^3} = k$ (k étant une constante), traduisant la troisième loi de Kepler.</t>
+  </si>
+  <si>
+    <t>3) Calculer alors la valeur de la masse $m_T$.</t>
+  </si>
+  <si>
+    <t>1) En appliquant la deuxième loi de Newton, établir l'équation différentielle vérifiée par l'abscisse $x(t)$.</t>
+  </si>
+  <si>
+    <t>2) La solution de cette équation différentielle s'écrit $x(t) = X_m \cos(\frac{2\pi}{T_0}t + \varphi)$ avec $T_0$ la période propre de l'oscillateur.</t>
+  </si>
+  <si>
+    <t>a) Déterminer les valeurs de : $T_0$, $X_m$, $\varphi$.</t>
+  </si>
+  <si>
+    <t>b) Déduire la valeur de la raideur K (On prend $\pi^2 = 10$).</t>
+  </si>
+  <si>
+    <t>3) Déterminer la variation de l'énergie potentielle élastique du système (solide (S) - ressort) entre les instants $t = 1 s$ et $t = 2,5 s$.</t>
+  </si>
+  <si>
+    <t>b) En exploitant la courbe de la figure 3, déterminer la valeur de la pseudopériode des oscillations.</t>
+  </si>
+  <si>
+    <t>c) En exploitant la courbe de la figure 3, déterminer le signe de l'intensité du courant $i$ entre l'instant $t_A$ et l'instant $t_B$.</t>
+  </si>
+  <si>
+    <t>d) Montrer que : $\frac{dE_T}{dt} = -ri^2$, avec $E_T$ l'énergie totale du circuit à un instant t.</t>
+  </si>
+  <si>
+    <t>e) Calculer $|E_{dh}|$ l'énergie dissipée par effet joule dans le circuit entre les instant $t=0$ et $t=t_A$.</t>
+  </si>
+  <si>
+    <t>1) Choisir parmi les affirmations suivantes l'affirmation juste : &lt;br&gt;
+&lt;br&gt;(A): Dans le noyau $^{107}_{48}Cd$ il y a 59 protons. &lt;br&gt;
+&lt;br&gt;(B): La désintégration d'un échantillon radioactif est d'autant plus rapide que sa constante radioactive $\lambda$ est plus petite. &lt;br&gt;
+&lt;br&gt;(C): Dans le diagramme (N, Z) de Segré, les isotopes sont sur une ligne perpendiculaire à l'axe des Z. &lt;br&gt;
 &lt;br&gt;(D): La cohésion du noyau est d'autant plus forte que son énergie de liaison par nucléon est petite.</t>
-  </si>
-  <si>
-    <t>1) Charge d'un condensateur par une source de courant. On veut déterminer la capacité $C_0$ d'un condensateur initialement déchargé. Le générateur de courant G débite un courant électrique d'intensité constante $I_0 = 1 \mu A$. A l'instant $t_0=0$, on met l'interrupteur K en position (1).</t>
-  </si>
-  <si>
-    <t>a) Exprimer la tension $u_c(t)$ en fonction de $I_0$, $C_0$ et $t$.</t>
-  </si>
-  <si>
-    <t>b) Vérifier que $C_0 = 1 \mu F$.</t>
-  </si>
-  <si>
-    <t>a) Établir l'équation différentielle vérifiée par $u_c(t)$.</t>
-  </si>
-  <si>
-    <t>2) Décharge d'un condensateur dans un dipôle RL. Lorsque la tension aux bornes du condensateur prend la valeur $u_C = U_0 = 10 V$, on bascule K en position (2) à un nouvel instant $t_0=0$.</t>
-  </si>
-  <si>
-    <t>3) Sélection et démodulation d'une onde modulée en amplitude. On utilise une chaine électronique pour sélectionner et démoduler une onde électromagnétique modulée en amplitude, avec une diode D idéale, la bobine (b) et le condensateur $C_0$.</t>
-  </si>
-  <si>
-    <t>a) Quel est le rôle de l'étage 2 ?</t>
-  </si>
-  <si>
-    <t>b) Trouver la valeur $C_1$ à laquelle il faut ajuster la capacité $C$ pour capter le signal modulé de fréquence $f_p = 162 kHz$ sachant que $L = 2 mH$ (on prend $\pi^2 = 10$).</t>
-  </si>
-  <si>
-    <t>c) La fréquence du signal modulant est $f_s = 5 kHz$. Si on ajuste R à la valeur $R_0 = 1,5 k\Omega$, aura-t-on une démodulation de bonne qualité ? Justifier.</t>
-  </si>
-  <si>
-    <t>1) Ecrire l'expression vectorielle de la force d'attraction gravitationnelle $\vec{F}$ exercée par la Terre sur (S) dans la base de Freinet $(\vec{u}; \vec{n})$.</t>
-  </si>
-  <si>
-    <t>2) En appliquant la deuxième loi de Newton:</t>
-  </si>
-  <si>
-    <t>a) Montrer que le mouvement circulaire du centre d'inertie $G_S$ autour de la Terre est uniforme.</t>
-  </si>
-  <si>
-    <t>b) Déterminer $V_S$ la norme de la vitesse de $G_S$ en fonction de $G$, $m_T$, $R_T$.</t>
-  </si>
-  <si>
-    <t>c) Déduire la relation : $\frac{T^2}{(R_T+h)^3} = k$ (k étant une constante), traduisant la troisième loi de Kepler.</t>
-  </si>
-  <si>
-    <t>3) Calculer alors la valeur de la masse $m_T$.</t>
-  </si>
-  <si>
-    <t>1) En appliquant la deuxième loi de Newton, établir l'équation différentielle vérifiée par l'abscisse $x(t)$.</t>
-  </si>
-  <si>
-    <t>2) La solution de cette équation différentielle s'écrit $x(t) = X_m \cos(\frac{2\pi}{T_0}t + \varphi)$ avec $T_0$ la période propre de l'oscillateur.</t>
-  </si>
-  <si>
-    <t>a) Déterminer les valeurs de : $T_0$, $X_m$, $\varphi$.</t>
-  </si>
-  <si>
-    <t>b) Déduire la valeur de la raideur K (On prend $\pi^2 = 10$).</t>
-  </si>
-  <si>
-    <t>3) Déterminer la variation de l'énergie potentielle élastique du système (solide (S) - ressort) entre les instants $t = 1 s$ et $t = 2,5 s$.</t>
-  </si>
-  <si>
-    <t>b) En exploitant la courbe de la figure 3, déterminer la valeur de la pseudopériode des oscillations.</t>
-  </si>
-  <si>
-    <t>c) En exploitant la courbe de la figure 3, déterminer le signe de l'intensité du courant $i$ entre l'instant $t_A$ et l'instant $t_B$.</t>
-  </si>
-  <si>
-    <t>d) Montrer que : $\frac{dE_T}{dt} = -ri^2$, avec $E_T$ l'énergie totale du circuit à un instant t.</t>
-  </si>
-  <si>
-    <t>e) Calculer $|E_{dh}|$ l'énergie dissipée par effet joule dans le circuit entre les instant $t=0$ et $t=t_A$.</t>
   </si>
 </sst>
 </file>
@@ -1221,7 +1221,7 @@
         <v>7</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
@@ -1405,10 +1405,10 @@
         <v>7</v>
       </c>
       <c r="D23" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>8</v>
@@ -1438,7 +1438,7 @@
         <v>7</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>8</v>
@@ -1468,10 +1468,10 @@
         <v>7</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>8</v>
@@ -1501,7 +1501,7 @@
         <v>7</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>8</v>
@@ -1531,7 +1531,7 @@
         <v>7</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>8</v>
@@ -1561,7 +1561,7 @@
         <v>7</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>8</v>
@@ -1621,10 +1621,10 @@
         <v>7</v>
       </c>
       <c r="D30" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>10</v>
@@ -1654,7 +1654,7 @@
         <v>7</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>9</v>
@@ -1684,7 +1684,7 @@
         <v>7</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
@@ -1772,7 +1772,7 @@
         <v>7</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3" t="s">
@@ -1803,10 +1803,10 @@
         <v>7</v>
       </c>
       <c r="D36" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>8</v>
@@ -1836,7 +1836,7 @@
         <v>7</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>9</v>
@@ -1866,7 +1866,7 @@
         <v>7</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>9</v>
@@ -1896,7 +1896,7 @@
         <v>7</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
@@ -1956,7 +1956,7 @@
         <v>7</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
@@ -1987,10 +1987,10 @@
         <v>7</v>
       </c>
       <c r="D42" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>9</v>
@@ -2022,7 +2022,7 @@
         <v>7</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>8</v>
@@ -2052,7 +2052,7 @@
         <v>7</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3" t="s">

--- a/PHY_SP_2025_N.xlsx
+++ b/PHY_SP_2025_N.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\BAC_SP_PREPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7830E9C3-26DA-4557-85AC-E15417EF22E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99E2B8A6-7563-48DD-B674-2913CDB121C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,14 +126,6 @@
  * le suivi cinétique d'une réaction d'estérification. </t>
   </si>
   <si>
-    <t>Partie 1: Dosage d'une solution aqueuse d'hydrogénosulfite de sodium. 
-L'hydrogénosulfite de sodium $NaHSO_3$ est utilisé pour le blanchiment de la pâte à papier. L'étiquette d'un flacon contenant une solution commerciale $(S_0)$ d'hydrogénosulfite de sodium $Na^+_{(aq)} + HSO^-_{3(aq)}$ porte l'indication : $500 g.L^{-1}$. La concentration molaire de $(S_0)$ est $C_0$. 
-&lt;br&gt;Données : Toutes les mesures sont effectuées à $25^{\circ}C$ ; Le produit ionique de l'eau : $K_e = 10^{-14}$ ; Masse molaire de l'hydrogénosulfite de sodium : $M(NaHSO_3) = 104 g.mol^{-1}$ ; Le couple acide/base : $HSO^-_{3(aq)} / SO^{2-}_{3(aq)}$ ; $pK_A(HSO^-_{3(aq)} / SO^{2-}_{3(aq)}) = 7,2$. 
-&lt;br&gt;Cette partie de l'exercice vise à vérifier par dosage acido-basique l'indication $500 g.L^{-1}$ inscrite sur l'étiquette de la solution commerciale. Pour vérifier cette indication, on procède comme suit : 
-On dilue 100 fois la solution $(S_0)$ de concentration molaire $C_0$ et on obtient ainsi une solution $(S_A)$ de concentration molaire $C_A$ ; 
-On prélève un volume $V_A = 20,0 mL$ de $(S_A)$ que l'on dose avec une solution aqueuse $(S_B)$ d'hydroxyde de sodium $Na^+_{(aq)} + HO^-_{(aq)}$ de concentration molaire $C_B = 0,10 mol.L^{-1}$. Le volume de la solution $(S_B)$ versé à l'équivalence est $V_{BE} = 9,6 mL$.</t>
-  </si>
-  <si>
     <t>Partie 2: Suivi cinétique d'une réaction d'estérification. 
 On étudie la cinétique de la réaction entre l'acide éthanoïque $CH_3COOH$ et le propan-1-ol $C_2H_5CH_2OH$. On réalise cette estérification dans différentes conditions expérimentales : 
 Expérience (1): On mélange $0,200 mol$ d'acide éthanoïque avec $0,200 mol$ du propan-1-ol à la température $\theta_1$. 
@@ -279,10 +271,18 @@
   </si>
   <si>
     <t>1) Choisir parmi les affirmations suivantes l'affirmation juste : &lt;br&gt;
-&lt;br&gt;(A): Dans le noyau $^{107}_{48}Cd$ il y a 59 protons. &lt;br&gt;
-&lt;br&gt;(B): La désintégration d'un échantillon radioactif est d'autant plus rapide que sa constante radioactive $\lambda$ est plus petite. &lt;br&gt;
-&lt;br&gt;(C): Dans le diagramme (N, Z) de Segré, les isotopes sont sur une ligne perpendiculaire à l'axe des Z. &lt;br&gt;
-&lt;br&gt;(D): La cohésion du noyau est d'autant plus forte que son énergie de liaison par nucléon est petite.</t>
+(A): Dans le noyau $^{107}_{48}Cd$ il y a 59 protons.
+(B): La désintégration d'un échantillon radioactif est d'autant plus rapide que sa constante radioactive $\lambda$ est plus petite.
+(C): Dans le diagramme de Segré, les isotopes sont sur une ligne perpendiculaire à l'axe des Z.
+(D): La cohésion du noyau est d'autant plus forte que son énergie de liaison par nucléon est petite.</t>
+  </si>
+  <si>
+    <t>Partie 1: Dosage d'une solution aqueuse d'hydrogénosulfite de sodium. 
+&lt;br&gt;L'hydrogénosulfite de sodium $NaHSO_3$ est utilisé pour le blanchiment de la pâte à papier. L'étiquette d'un flacon contenant une solution commerciale $(S_0)$ d'hydrogénosulfite de sodium $Na^+_{(aq)} + HSO^-_{3(aq)}$ porte l'indication : $500 g.L^{-1}$. La concentration molaire de $(S_0)$ est $C_0$. 
+&lt;br&gt;Données : Toutes les mesures sont effectuées à $25^{\circ}C$ ; Le produit ionique de l'eau : $K_e = 10^{-14}$ ; Masse molaire de l'hydrogénosulfite de sodium : $M(NaHSO_3) = 104 g.mol^{-1}$ ; Le couple acide/base : $HSO^-_{3(aq)} / SO^{2-}_{3(aq)}$ ; $pK_A(HSO^-_{3(aq)} / SO^{2-}_{3(aq)}) = 7,2$. 
+&lt;br&gt;Cette partie de l'exercice vise à vérifier par dosage acido-basique l'indication $500 g.L^{-1}$ inscrite sur l'étiquette de la solution commerciale. Pour vérifier cette indication, on procède comme suit : 
+On dilue 100 fois la solution $(S_0)$ de concentration molaire $C_0$ et on obtient ainsi une solution $(S_A)$ de concentration molaire $C_A$ ; 
+On prélève un volume $V_A = 20,0 mL$ de $(S_A)$ que l'on dose avec une solution aqueuse $(S_B)$ d'hydroxyde de sodium $Na^+_{(aq)} + HO^-_{(aq)}$ de concentration molaire $C_B = 0,10 mol.L^{-1}$. Le volume de la solution $(S_B)$ versé à l'équivalence est $V_{BE} = 9,6 mL$.</t>
   </si>
 </sst>
 </file>
@@ -759,13 +759,13 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -788,17 +788,17 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="255" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>32</v>
+      <c r="D3" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -823,14 +823,14 @@
       <c r="B4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>8</v>
@@ -856,11 +856,11 @@
       <c r="B5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>9</v>
@@ -886,11 +886,11 @@
       <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>10</v>
@@ -916,11 +916,11 @@
       <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>9</v>
@@ -946,11 +946,11 @@
       <c r="B8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>9</v>
@@ -976,11 +976,11 @@
       <c r="B9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>9</v>
@@ -1000,17 +1000,17 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="150" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -1035,14 +1035,14 @@
       <c r="B11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>9</v>
@@ -1068,11 +1068,11 @@
       <c r="B12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1098,11 +1098,11 @@
       <c r="B13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>9</v>
@@ -1128,11 +1128,11 @@
       <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>9</v>
@@ -1158,11 +1158,11 @@
       <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>8</v>
@@ -1182,17 +1182,17 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="90" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -1210,18 +1210,18 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
@@ -1248,11 +1248,11 @@
       <c r="B18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
@@ -1273,20 +1273,20 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>8</v>
@@ -1312,11 +1312,11 @@
       <c r="B20" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>8</v>
@@ -1342,11 +1342,11 @@
       <c r="B21" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>8</v>
@@ -1366,17 +1366,17 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -1395,20 +1395,20 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>8</v>
@@ -1434,11 +1434,11 @@
       <c r="B24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>8</v>
@@ -1464,14 +1464,14 @@
       <c r="B25" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>8</v>
@@ -1497,11 +1497,11 @@
       <c r="B26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>8</v>
@@ -1527,11 +1527,11 @@
       <c r="B27" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>8</v>
@@ -1557,11 +1557,11 @@
       <c r="B28" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>8</v>
@@ -1587,11 +1587,11 @@
       <c r="B29" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>8</v>
@@ -1611,20 +1611,20 @@
       </c>
     </row>
     <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D30" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>10</v>
@@ -1650,11 +1650,11 @@
       <c r="B31" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>9</v>
@@ -1680,11 +1680,11 @@
       <c r="B32" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
@@ -1704,13 +1704,13 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D33" s="7" t="s">
@@ -1733,13 +1733,13 @@
       </c>
     </row>
     <row r="34" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D34" s="2" t="s">
@@ -1768,11 +1768,11 @@
       <c r="B35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3" t="s">
@@ -1793,20 +1793,20 @@
       </c>
     </row>
     <row r="36" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D36" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>8</v>
@@ -1832,11 +1832,11 @@
       <c r="B37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>9</v>
@@ -1862,11 +1862,11 @@
       <c r="B38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>9</v>
@@ -1892,11 +1892,11 @@
       <c r="B39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
@@ -1917,13 +1917,13 @@
       </c>
     </row>
     <row r="40" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D40" s="2" t="s">
@@ -1952,11 +1952,11 @@
       <c r="B41" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
@@ -1977,20 +1977,20 @@
       </c>
     </row>
     <row r="42" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D42" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>9</v>
@@ -2018,11 +2018,11 @@
       <c r="B43" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>8</v>
@@ -2048,11 +2048,11 @@
       <c r="B44" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3" t="s">

--- a/PHY_SP_2025_N.xlsx
+++ b/PHY_SP_2025_N.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\BAC_SP_PREPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99E2B8A6-7563-48DD-B674-2913CDB121C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6C54B2-E7E9-4D56-B1DC-9F514D72FBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -258,23 +258,10 @@
     <t>3) Déterminer la variation de l'énergie potentielle élastique du système (solide (S) - ressort) entre les instants $t = 1 s$ et $t = 2,5 s$.</t>
   </si>
   <si>
-    <t>b) En exploitant la courbe de la figure 3, déterminer la valeur de la pseudopériode des oscillations.</t>
-  </si>
-  <si>
-    <t>c) En exploitant la courbe de la figure 3, déterminer le signe de l'intensité du courant $i$ entre l'instant $t_A$ et l'instant $t_B$.</t>
-  </si>
-  <si>
     <t>d) Montrer que : $\frac{dE_T}{dt} = -ri^2$, avec $E_T$ l'énergie totale du circuit à un instant t.</t>
   </si>
   <si>
     <t>e) Calculer $|E_{dh}|$ l'énergie dissipée par effet joule dans le circuit entre les instant $t=0$ et $t=t_A$.</t>
-  </si>
-  <si>
-    <t>1) Choisir parmi les affirmations suivantes l'affirmation juste : &lt;br&gt;
-(A): Dans le noyau $^{107}_{48}Cd$ il y a 59 protons.
-(B): La désintégration d'un échantillon radioactif est d'autant plus rapide que sa constante radioactive $\lambda$ est plus petite.
-(C): Dans le diagramme de Segré, les isotopes sont sur une ligne perpendiculaire à l'axe des Z.
-(D): La cohésion du noyau est d'autant plus forte que son énergie de liaison par nucléon est petite.</t>
   </si>
   <si>
     <t>Partie 1: Dosage d'une solution aqueuse d'hydrogénosulfite de sodium. 
@@ -283,6 +270,19 @@
 &lt;br&gt;Cette partie de l'exercice vise à vérifier par dosage acido-basique l'indication $500 g.L^{-1}$ inscrite sur l'étiquette de la solution commerciale. Pour vérifier cette indication, on procède comme suit : 
 On dilue 100 fois la solution $(S_0)$ de concentration molaire $C_0$ et on obtient ainsi une solution $(S_A)$ de concentration molaire $C_A$ ; 
 On prélève un volume $V_A = 20,0 mL$ de $(S_A)$ que l'on dose avec une solution aqueuse $(S_B)$ d'hydroxyde de sodium $Na^+_{(aq)} + HO^-_{(aq)}$ de concentration molaire $C_B = 0,10 mol.L^{-1}$. Le volume de la solution $(S_B)$ versé à l'équivalence est $V_{BE} = 9,6 mL$.</t>
+  </si>
+  <si>
+    <t>1) Choisir parmi les affirmations suivantes l'affirmation juste : &lt;br&gt;
+(A): Dans le noyau $^{107}_{48}Cd$ il y a 59 protons.
+(B): La désintégration d'un échantillon radioactif est d'autant plus rapide que sa constante radioactive $\lambda$ est plus petite.
+(C): Dans le diagramme de Segré $(N,Z)$, les isotopes sont sur une ligne perpendiculaire à l'axe des Z.
+(D): La cohésion du noyau est d'autant plus forte que son énergie de liaison par nucléon est petite.</t>
+  </si>
+  <si>
+    <t>b-1) En exploitant la courbe de la figure 3, déterminer la valeur de la pseudopériode des oscillations.</t>
+  </si>
+  <si>
+    <t>b-2) En exploitant la courbe de la figure 3, déterminer le signe de l'intensité du courant $i$ entre l'instant $t_A$ et l'instant $t_B$.</t>
   </si>
 </sst>
 </file>
@@ -798,7 +798,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -1210,7 +1210,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>11</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>7</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
@@ -1501,7 +1501,7 @@
         <v>7</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>8</v>
@@ -1531,7 +1531,7 @@
         <v>7</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>8</v>
@@ -1561,7 +1561,7 @@
         <v>7</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>8</v>

--- a/PHY_SP_2025_N.xlsx
+++ b/PHY_SP_2025_N.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\BAC_SP_PREPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6C54B2-E7E9-4D56-B1DC-9F514D72FBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB4E7F1-7470-487A-B100-1A8E0E679DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -279,10 +279,10 @@
 (D): La cohésion du noyau est d'autant plus forte que son énergie de liaison par nucléon est petite.</t>
   </si>
   <si>
-    <t>b-1) En exploitant la courbe de la figure 3, déterminer la valeur de la pseudopériode des oscillations.</t>
-  </si>
-  <si>
-    <t>b-2) En exploitant la courbe de la figure 3, déterminer le signe de l'intensité du courant $i$ entre l'instant $t_A$ et l'instant $t_B$.</t>
+    <t>b) En exploitant la courbe de la figure 3, déterminer la valeur de la pseudopériode des oscillations.</t>
+  </si>
+  <si>
+    <t>c) En exploitant la courbe de la figure 3, déterminer le signe de l'intensité du courant $i$ entre l'instant $t_A$ et l'instant $t_B$.</t>
   </si>
 </sst>
 </file>
